--- a/public/templates/03_거래처_서류_일괄생성/거래처_서류_일괄생성.xlsx
+++ b/public/templates/03_거래처_서류_일괄생성/거래처_서류_일괄생성.xlsx
@@ -2758,36 +2758,56 @@
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="11"/>
-      <c r="B3" s="17"/>
-      <c r="C3" s="12"/>
-      <c r="D3" s="12"/>
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>2026-0001</t>
+        </is>
+      </c>
+      <c r="B3" s="17" t="n">
+        <v>46267</v>
+      </c>
+      <c r="C3" s="12" t="inlineStr">
+        <is>
+          <t>○○전자</t>
+        </is>
+      </c>
+      <c r="D3" s="12" t="inlineStr">
+        <is>
+          <t>제어반 ASSY</t>
+        </is>
+      </c>
       <c r="E3" s="18" t="str">
         <f aca="false">IF($D3="","",IFERROR(INDEX(품목마스터!$B$3:$B$102,MATCH($D3,품목마스터!$A$3:$A$102,0)),""))</f>
-        <v/>
+        <v>CP-200</v>
       </c>
       <c r="F3" s="18" t="str">
         <f aca="false">IF($D3="","",IFERROR(INDEX(품목마스터!$C$3:$C$102,MATCH($D3,품목마스터!$A$3:$A$102,0)),""))</f>
-        <v/>
-      </c>
-      <c r="G3" s="13" t="str">
+        <v>EA</v>
+      </c>
+      <c r="G3" s="13" t="n">
         <f aca="false">IF($D3="","",IFERROR(INDEX(품목마스터!$D$3:$D$102,MATCH($D3,품목마스터!$A$3:$A$102,0)),0))</f>
-        <v/>
-      </c>
-      <c r="H3" s="11"/>
-      <c r="I3" s="19" t="str">
+        <v>320000</v>
+      </c>
+      <c r="H3" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="I3" s="19" t="n">
         <f aca="false">IF(OR($G3="",$H3=""),"",ROUND($G3*$H3,0))</f>
-        <v/>
-      </c>
-      <c r="J3" s="12"/>
+        <v>960000</v>
+      </c>
+      <c r="J3" s="12" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="K3" s="11"/>
-      <c r="L3" s="18" t="str">
+      <c r="L3" s="18" t="n">
         <f aca="false">IF($A3="","",COUNTIFS($A$3:$A3,$A3))</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="M3" s="18" t="str">
         <f aca="false">IF($A3="","",$A3&amp;"|"&amp;$L3)</f>
-        <v/>
+        <v>2026-0001|1</v>
       </c>
       <c r="N3" s="18" t="str">
         <f aca="false">IF(OR($A3="",UPPER($J3)&lt;&gt;"Y"),"",$A3&amp;"#"&amp;COUNTIFS($A$3:$A3,$A3,$J$3:$J3,"Y"))</f>
@@ -2795,36 +2815,56 @@
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="11"/>
-      <c r="B4" s="17"/>
-      <c r="C4" s="12"/>
-      <c r="D4" s="12"/>
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>2026-0001</t>
+        </is>
+      </c>
+      <c r="B4" s="17" t="n">
+        <v>46267</v>
+      </c>
+      <c r="C4" s="12" t="inlineStr">
+        <is>
+          <t>○○전자</t>
+        </is>
+      </c>
+      <c r="D4" s="12" t="inlineStr">
+        <is>
+          <t>센서 모듈</t>
+        </is>
+      </c>
       <c r="E4" s="18" t="str">
         <f aca="false">IF($D4="","",IFERROR(INDEX(품목마스터!$B$3:$B$102,MATCH($D4,품목마스터!$A$3:$A$102,0)),""))</f>
-        <v/>
+        <v>SM-15</v>
       </c>
       <c r="F4" s="18" t="str">
         <f aca="false">IF($D4="","",IFERROR(INDEX(품목마스터!$C$3:$C$102,MATCH($D4,품목마스터!$A$3:$A$102,0)),""))</f>
-        <v/>
-      </c>
-      <c r="G4" s="13" t="str">
+        <v>EA</v>
+      </c>
+      <c r="G4" s="13" t="n">
         <f aca="false">IF($D4="","",IFERROR(INDEX(품목마스터!$D$3:$D$102,MATCH($D4,품목마스터!$A$3:$A$102,0)),0))</f>
-        <v/>
-      </c>
-      <c r="H4" s="11"/>
-      <c r="I4" s="19" t="str">
+        <v>45000</v>
+      </c>
+      <c r="H4" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="I4" s="19" t="n">
         <f aca="false">IF(OR($G4="",$H4=""),"",ROUND($G4*$H4,0))</f>
-        <v/>
-      </c>
-      <c r="J4" s="12"/>
+        <v>540000</v>
+      </c>
+      <c r="J4" s="12" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="K4" s="11"/>
-      <c r="L4" s="18" t="str">
+      <c r="L4" s="18" t="n">
         <f aca="false">IF($A4="","",COUNTIFS($A$3:$A4,$A4))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="M4" s="18" t="str">
         <f aca="false">IF($A4="","",$A4&amp;"|"&amp;$L4)</f>
-        <v/>
+        <v>2026-0001|2</v>
       </c>
       <c r="N4" s="18" t="str">
         <f aca="false">IF(OR($A4="",UPPER($J4)&lt;&gt;"Y"),"",$A4&amp;"#"&amp;COUNTIFS($A$3:$A4,$A4,$J$3:$J4,"Y"))</f>
@@ -2832,36 +2872,56 @@
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="11"/>
-      <c r="B5" s="17"/>
-      <c r="C5" s="12"/>
-      <c r="D5" s="12"/>
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>2026-0001</t>
+        </is>
+      </c>
+      <c r="B5" s="17" t="n">
+        <v>46267</v>
+      </c>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
+          <t>○○전자</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="inlineStr">
+        <is>
+          <t>케이블 하네스</t>
+        </is>
+      </c>
       <c r="E5" s="18" t="str">
         <f aca="false">IF($D5="","",IFERROR(INDEX(품목마스터!$B$3:$B$102,MATCH($D5,품목마스터!$A$3:$A$102,0)),""))</f>
-        <v/>
+        <v>2M</v>
       </c>
       <c r="F5" s="18" t="str">
         <f aca="false">IF($D5="","",IFERROR(INDEX(품목마스터!$C$3:$C$102,MATCH($D5,품목마스터!$A$3:$A$102,0)),""))</f>
-        <v/>
-      </c>
-      <c r="G5" s="13" t="str">
+        <v>SET</v>
+      </c>
+      <c r="G5" s="13" t="n">
         <f aca="false">IF($D5="","",IFERROR(INDEX(품목마스터!$D$3:$D$102,MATCH($D5,품목마스터!$A$3:$A$102,0)),0))</f>
-        <v/>
-      </c>
-      <c r="H5" s="11"/>
-      <c r="I5" s="19" t="str">
+        <v>28000</v>
+      </c>
+      <c r="H5" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="I5" s="19" t="n">
         <f aca="false">IF(OR($G5="",$H5=""),"",ROUND($G5*$H5,0))</f>
-        <v/>
-      </c>
-      <c r="J5" s="12"/>
+        <v>168000</v>
+      </c>
+      <c r="J5" s="12" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="K5" s="11"/>
-      <c r="L5" s="18" t="str">
+      <c r="L5" s="18" t="n">
         <f aca="false">IF($A5="","",COUNTIFS($A$3:$A5,$A5))</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="M5" s="18" t="str">
         <f aca="false">IF($A5="","",$A5&amp;"|"&amp;$L5)</f>
-        <v/>
+        <v>2026-0001|3</v>
       </c>
       <c r="N5" s="18" t="str">
         <f aca="false">IF(OR($A5="",UPPER($J5)&lt;&gt;"Y"),"",$A5&amp;"#"&amp;COUNTIFS($A$3:$A5,$A5,$J$3:$J5,"Y"))</f>
@@ -2869,40 +2929,64 @@
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="11"/>
-      <c r="B6" s="17"/>
-      <c r="C6" s="12"/>
-      <c r="D6" s="12"/>
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>2026-0002</t>
+        </is>
+      </c>
+      <c r="B6" s="17" t="n">
+        <v>46273</v>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>○○전자</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>센서 모듈</t>
+        </is>
+      </c>
       <c r="E6" s="18" t="str">
         <f aca="false">IF($D6="","",IFERROR(INDEX(품목마스터!$B$3:$B$102,MATCH($D6,품목마스터!$A$3:$A$102,0)),""))</f>
-        <v/>
+        <v>SM-15</v>
       </c>
       <c r="F6" s="18" t="str">
         <f aca="false">IF($D6="","",IFERROR(INDEX(품목마스터!$C$3:$C$102,MATCH($D6,품목마스터!$A$3:$A$102,0)),""))</f>
-        <v/>
-      </c>
-      <c r="G6" s="13" t="str">
+        <v>EA</v>
+      </c>
+      <c r="G6" s="13" t="n">
         <f aca="false">IF($D6="","",IFERROR(INDEX(품목마스터!$D$3:$D$102,MATCH($D6,품목마스터!$A$3:$A$102,0)),0))</f>
-        <v/>
-      </c>
-      <c r="H6" s="11"/>
-      <c r="I6" s="19" t="str">
+        <v>45000</v>
+      </c>
+      <c r="H6" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="I6" s="19" t="n">
         <f aca="false">IF(OR($G6="",$H6=""),"",ROUND($G6*$H6,0))</f>
-        <v/>
-      </c>
-      <c r="J6" s="12"/>
-      <c r="K6" s="11"/>
-      <c r="L6" s="18" t="str">
+        <v>180000</v>
+      </c>
+      <c r="J6" s="12" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="K6" s="11" t="inlineStr">
+        <is>
+          <t>초기 불량 교체 요청</t>
+        </is>
+      </c>
+      <c r="L6" s="18" t="n">
         <f aca="false">IF($A6="","",COUNTIFS($A$3:$A6,$A6))</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="M6" s="18" t="str">
         <f aca="false">IF($A6="","",$A6&amp;"|"&amp;$L6)</f>
-        <v/>
+        <v>2026-0002|1</v>
       </c>
       <c r="N6" s="18" t="str">
         <f aca="false">IF(OR($A6="",UPPER($J6)&lt;&gt;"Y"),"",$A6&amp;"#"&amp;COUNTIFS($A$3:$A6,$A6,$J$3:$J6,"Y"))</f>
-        <v/>
+        <v>2026-0002#1</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13925,9 +14009,9 @@
       <c r="E3" s="21" t="s">
         <v>62</v>
       </c>
-      <c r="F3" s="23" t="str">
+      <c r="F3" s="23" t="n">
         <f aca="false">IFERROR(INDEX(출고현황!$B$3:$B$302,MATCH($C$3,출고현황!$A$3:$A$302,0)),"")</f>
-        <v/>
+        <v>46267</v>
       </c>
       <c r="G3" s="23"/>
     </row>
@@ -13949,7 +14033,7 @@
       <c r="B6" s="25"/>
       <c r="C6" s="18" t="str">
         <f aca="false">IFERROR(INDEX(출고현황!$C$3:$C$302,MATCH($C$3,출고현황!$A$3:$A$302,0)),"")</f>
-        <v/>
+        <v>○○전자</v>
       </c>
       <c r="D6" s="18"/>
       <c r="E6" s="25" t="s">
@@ -13968,7 +14052,7 @@
       <c r="B7" s="25"/>
       <c r="C7" s="18" t="str">
         <f aca="false">IFERROR(INDEX(거래처목록!$B$3:$B$62,MATCH($C$6,거래처목록!$A$3:$A$62,0)),"")</f>
-        <v/>
+        <v>111-11-11111</v>
       </c>
       <c r="D7" s="18"/>
       <c r="E7" s="25" t="s">
@@ -13987,7 +14071,7 @@
       <c r="B8" s="25"/>
       <c r="C8" s="18" t="str">
         <f aca="false">IFERROR(INDEX(거래처목록!$E$3:$E$62,MATCH($C$6,거래처목록!$A$3:$A$62,0)),"")</f>
-        <v/>
+        <v>박과장</v>
       </c>
       <c r="D8" s="18"/>
       <c r="E8" s="25" t="s">
@@ -14028,27 +14112,27 @@
       </c>
       <c r="B11" s="18" t="str">
         <f aca="false">IFERROR(INDEX(출고현황!$D$3:$D$302,MATCH($C$3&amp;"|"&amp;1,출고현황!$M$3:$M$302,0)),"")</f>
-        <v/>
+        <v>제어반 ASSY</v>
       </c>
       <c r="C11" s="18" t="str">
         <f aca="false">IF($B11="","",IFERROR(INDEX(출고현황!$E$3:$E$302,MATCH($C$3&amp;"|"&amp;1,출고현황!$M$3:$M$302,0)),""))</f>
-        <v/>
+        <v>CP-200</v>
       </c>
       <c r="D11" s="28" t="str">
         <f aca="false">IF($B11="","",IFERROR(INDEX(출고현황!$F$3:$F$302,MATCH($C$3&amp;"|"&amp;1,출고현황!$M$3:$M$302,0)),""))</f>
-        <v/>
-      </c>
-      <c r="E11" s="29" t="str">
+        <v>EA</v>
+      </c>
+      <c r="E11" s="29" t="n">
         <f aca="false">IF($B11="","",IFERROR(INDEX(출고현황!$H$3:$H$302,MATCH($C$3&amp;"|"&amp;1,출고현황!$M$3:$M$302,0)),""))</f>
-        <v/>
-      </c>
-      <c r="F11" s="19" t="str">
+        <v>3</v>
+      </c>
+      <c r="F11" s="19" t="n">
         <f aca="false">IF($B11="","",IFERROR(INDEX(출고현황!$G$3:$G$302,MATCH($C$3&amp;"|"&amp;1,출고현황!$M$3:$M$302,0)),""))</f>
-        <v/>
-      </c>
-      <c r="G11" s="19" t="str">
+        <v>320000</v>
+      </c>
+      <c r="G11" s="19" t="n">
         <f aca="false">IF($B11="","",IFERROR(INDEX(출고현황!$I$3:$I$302,MATCH($C$3&amp;"|"&amp;1,출고현황!$M$3:$M$302,0)),""))</f>
-        <v/>
+        <v>960000</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14057,27 +14141,27 @@
       </c>
       <c r="B12" s="18" t="str">
         <f aca="false">IFERROR(INDEX(출고현황!$D$3:$D$302,MATCH($C$3&amp;"|"&amp;2,출고현황!$M$3:$M$302,0)),"")</f>
-        <v/>
+        <v>센서 모듈</v>
       </c>
       <c r="C12" s="18" t="str">
         <f aca="false">IF($B12="","",IFERROR(INDEX(출고현황!$E$3:$E$302,MATCH($C$3&amp;"|"&amp;2,출고현황!$M$3:$M$302,0)),""))</f>
-        <v/>
+        <v>SM-15</v>
       </c>
       <c r="D12" s="28" t="str">
         <f aca="false">IF($B12="","",IFERROR(INDEX(출고현황!$F$3:$F$302,MATCH($C$3&amp;"|"&amp;2,출고현황!$M$3:$M$302,0)),""))</f>
-        <v/>
-      </c>
-      <c r="E12" s="29" t="str">
+        <v>EA</v>
+      </c>
+      <c r="E12" s="29" t="n">
         <f aca="false">IF($B12="","",IFERROR(INDEX(출고현황!$H$3:$H$302,MATCH($C$3&amp;"|"&amp;2,출고현황!$M$3:$M$302,0)),""))</f>
-        <v/>
-      </c>
-      <c r="F12" s="19" t="str">
+        <v>12</v>
+      </c>
+      <c r="F12" s="19" t="n">
         <f aca="false">IF($B12="","",IFERROR(INDEX(출고현황!$G$3:$G$302,MATCH($C$3&amp;"|"&amp;2,출고현황!$M$3:$M$302,0)),""))</f>
-        <v/>
-      </c>
-      <c r="G12" s="19" t="str">
+        <v>45000</v>
+      </c>
+      <c r="G12" s="19" t="n">
         <f aca="false">IF($B12="","",IFERROR(INDEX(출고현황!$I$3:$I$302,MATCH($C$3&amp;"|"&amp;2,출고현황!$M$3:$M$302,0)),""))</f>
-        <v/>
+        <v>540000</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14086,27 +14170,27 @@
       </c>
       <c r="B13" s="18" t="str">
         <f aca="false">IFERROR(INDEX(출고현황!$D$3:$D$302,MATCH($C$3&amp;"|"&amp;3,출고현황!$M$3:$M$302,0)),"")</f>
-        <v/>
+        <v>케이블 하네스</v>
       </c>
       <c r="C13" s="18" t="str">
         <f aca="false">IF($B13="","",IFERROR(INDEX(출고현황!$E$3:$E$302,MATCH($C$3&amp;"|"&amp;3,출고현황!$M$3:$M$302,0)),""))</f>
-        <v/>
+        <v>2M</v>
       </c>
       <c r="D13" s="28" t="str">
         <f aca="false">IF($B13="","",IFERROR(INDEX(출고현황!$F$3:$F$302,MATCH($C$3&amp;"|"&amp;3,출고현황!$M$3:$M$302,0)),""))</f>
-        <v/>
-      </c>
-      <c r="E13" s="29" t="str">
+        <v>SET</v>
+      </c>
+      <c r="E13" s="29" t="n">
         <f aca="false">IF($B13="","",IFERROR(INDEX(출고현황!$H$3:$H$302,MATCH($C$3&amp;"|"&amp;3,출고현황!$M$3:$M$302,0)),""))</f>
-        <v/>
-      </c>
-      <c r="F13" s="19" t="str">
+        <v>6</v>
+      </c>
+      <c r="F13" s="19" t="n">
         <f aca="false">IF($B13="","",IFERROR(INDEX(출고현황!$G$3:$G$302,MATCH($C$3&amp;"|"&amp;3,출고현황!$M$3:$M$302,0)),""))</f>
-        <v/>
-      </c>
-      <c r="G13" s="19" t="str">
+        <v>28000</v>
+      </c>
+      <c r="G13" s="19" t="n">
         <f aca="false">IF($B13="","",IFERROR(INDEX(출고현황!$I$3:$I$302,MATCH($C$3&amp;"|"&amp;3,출고현황!$M$3:$M$302,0)),""))</f>
-        <v/>
+        <v>168000</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14554,7 +14638,7 @@
       <c r="F29" s="25"/>
       <c r="G29" s="30" t="n">
         <f aca="false">SUM(G11:G28)</f>
-        <v>0</v>
+        <v>1668000</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14567,7 +14651,7 @@
       <c r="F30" s="25"/>
       <c r="G30" s="30" t="n">
         <f aca="false">ROUND(G29*기초정보!$C$11,0)</f>
-        <v>0</v>
+        <v>166800</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14580,7 +14664,7 @@
       <c r="F31" s="31"/>
       <c r="G31" s="32" t="n">
         <f aca="false">G29+G30</f>
-        <v>0</v>
+        <v>1834800</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14664,9 +14748,9 @@
       <c r="E3" s="21" t="s">
         <v>62</v>
       </c>
-      <c r="F3" s="23" t="str">
+      <c r="F3" s="23" t="n">
         <f aca="false">IFERROR(INDEX(출고현황!$B$3:$B$302,MATCH($C$3,출고현황!$A$3:$A$302,0)),"")</f>
-        <v/>
+        <v>46267</v>
       </c>
       <c r="G3" s="23"/>
     </row>
@@ -14688,7 +14772,7 @@
       <c r="B6" s="25"/>
       <c r="C6" s="18" t="str">
         <f aca="false">IFERROR(INDEX(출고현황!$C$3:$C$302,MATCH($C$3,출고현황!$A$3:$A$302,0)),"")</f>
-        <v/>
+        <v>○○전자</v>
       </c>
       <c r="D6" s="18"/>
       <c r="E6" s="25" t="s">
@@ -14707,7 +14791,7 @@
       <c r="B7" s="25"/>
       <c r="C7" s="18" t="str">
         <f aca="false">IFERROR(INDEX(거래처목록!$B$3:$B$62,MATCH($C$6,거래처목록!$A$3:$A$62,0)),"")</f>
-        <v/>
+        <v>111-11-11111</v>
       </c>
       <c r="D7" s="18"/>
       <c r="E7" s="25" t="s">
@@ -14726,7 +14810,7 @@
       <c r="B8" s="25"/>
       <c r="C8" s="18" t="str">
         <f aca="false">IFERROR(INDEX(거래처목록!$E$3:$E$62,MATCH($C$6,거래처목록!$A$3:$A$62,0)),"")</f>
-        <v/>
+        <v>박과장</v>
       </c>
       <c r="D8" s="18"/>
       <c r="E8" s="25" t="s">
@@ -14767,27 +14851,27 @@
       </c>
       <c r="B11" s="18" t="str">
         <f aca="false">IFERROR(INDEX(출고현황!$D$3:$D$302,MATCH($C$3&amp;"|"&amp;1,출고현황!$M$3:$M$302,0)),"")</f>
-        <v/>
+        <v>제어반 ASSY</v>
       </c>
       <c r="C11" s="18" t="str">
         <f aca="false">IF($B11="","",IFERROR(INDEX(출고현황!$E$3:$E$302,MATCH($C$3&amp;"|"&amp;1,출고현황!$M$3:$M$302,0)),""))</f>
-        <v/>
+        <v>CP-200</v>
       </c>
       <c r="D11" s="28" t="str">
         <f aca="false">IF($B11="","",IFERROR(INDEX(출고현황!$F$3:$F$302,MATCH($C$3&amp;"|"&amp;1,출고현황!$M$3:$M$302,0)),""))</f>
-        <v/>
-      </c>
-      <c r="E11" s="29" t="str">
+        <v>EA</v>
+      </c>
+      <c r="E11" s="29" t="n">
         <f aca="false">IF($B11="","",IFERROR(INDEX(출고현황!$H$3:$H$302,MATCH($C$3&amp;"|"&amp;1,출고현황!$M$3:$M$302,0)),""))</f>
-        <v/>
-      </c>
-      <c r="F11" s="19" t="str">
+        <v>3</v>
+      </c>
+      <c r="F11" s="19" t="n">
         <f aca="false">IF($B11="","",IFERROR(INDEX(출고현황!$G$3:$G$302,MATCH($C$3&amp;"|"&amp;1,출고현황!$M$3:$M$302,0)),""))</f>
-        <v/>
-      </c>
-      <c r="G11" s="19" t="str">
+        <v>320000</v>
+      </c>
+      <c r="G11" s="19" t="n">
         <f aca="false">IF($B11="","",IFERROR(INDEX(출고현황!$I$3:$I$302,MATCH($C$3&amp;"|"&amp;1,출고현황!$M$3:$M$302,0)),""))</f>
-        <v/>
+        <v>960000</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14796,27 +14880,27 @@
       </c>
       <c r="B12" s="18" t="str">
         <f aca="false">IFERROR(INDEX(출고현황!$D$3:$D$302,MATCH($C$3&amp;"|"&amp;2,출고현황!$M$3:$M$302,0)),"")</f>
-        <v/>
+        <v>센서 모듈</v>
       </c>
       <c r="C12" s="18" t="str">
         <f aca="false">IF($B12="","",IFERROR(INDEX(출고현황!$E$3:$E$302,MATCH($C$3&amp;"|"&amp;2,출고현황!$M$3:$M$302,0)),""))</f>
-        <v/>
+        <v>SM-15</v>
       </c>
       <c r="D12" s="28" t="str">
         <f aca="false">IF($B12="","",IFERROR(INDEX(출고현황!$F$3:$F$302,MATCH($C$3&amp;"|"&amp;2,출고현황!$M$3:$M$302,0)),""))</f>
-        <v/>
-      </c>
-      <c r="E12" s="29" t="str">
+        <v>EA</v>
+      </c>
+      <c r="E12" s="29" t="n">
         <f aca="false">IF($B12="","",IFERROR(INDEX(출고현황!$H$3:$H$302,MATCH($C$3&amp;"|"&amp;2,출고현황!$M$3:$M$302,0)),""))</f>
-        <v/>
-      </c>
-      <c r="F12" s="19" t="str">
+        <v>12</v>
+      </c>
+      <c r="F12" s="19" t="n">
         <f aca="false">IF($B12="","",IFERROR(INDEX(출고현황!$G$3:$G$302,MATCH($C$3&amp;"|"&amp;2,출고현황!$M$3:$M$302,0)),""))</f>
-        <v/>
-      </c>
-      <c r="G12" s="19" t="str">
+        <v>45000</v>
+      </c>
+      <c r="G12" s="19" t="n">
         <f aca="false">IF($B12="","",IFERROR(INDEX(출고현황!$I$3:$I$302,MATCH($C$3&amp;"|"&amp;2,출고현황!$M$3:$M$302,0)),""))</f>
-        <v/>
+        <v>540000</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14825,27 +14909,27 @@
       </c>
       <c r="B13" s="18" t="str">
         <f aca="false">IFERROR(INDEX(출고현황!$D$3:$D$302,MATCH($C$3&amp;"|"&amp;3,출고현황!$M$3:$M$302,0)),"")</f>
-        <v/>
+        <v>케이블 하네스</v>
       </c>
       <c r="C13" s="18" t="str">
         <f aca="false">IF($B13="","",IFERROR(INDEX(출고현황!$E$3:$E$302,MATCH($C$3&amp;"|"&amp;3,출고현황!$M$3:$M$302,0)),""))</f>
-        <v/>
+        <v>2M</v>
       </c>
       <c r="D13" s="28" t="str">
         <f aca="false">IF($B13="","",IFERROR(INDEX(출고현황!$F$3:$F$302,MATCH($C$3&amp;"|"&amp;3,출고현황!$M$3:$M$302,0)),""))</f>
-        <v/>
-      </c>
-      <c r="E13" s="29" t="str">
+        <v>SET</v>
+      </c>
+      <c r="E13" s="29" t="n">
         <f aca="false">IF($B13="","",IFERROR(INDEX(출고현황!$H$3:$H$302,MATCH($C$3&amp;"|"&amp;3,출고현황!$M$3:$M$302,0)),""))</f>
-        <v/>
-      </c>
-      <c r="F13" s="19" t="str">
+        <v>6</v>
+      </c>
+      <c r="F13" s="19" t="n">
         <f aca="false">IF($B13="","",IFERROR(INDEX(출고현황!$G$3:$G$302,MATCH($C$3&amp;"|"&amp;3,출고현황!$M$3:$M$302,0)),""))</f>
-        <v/>
-      </c>
-      <c r="G13" s="19" t="str">
+        <v>28000</v>
+      </c>
+      <c r="G13" s="19" t="n">
         <f aca="false">IF($B13="","",IFERROR(INDEX(출고현황!$I$3:$I$302,MATCH($C$3&amp;"|"&amp;3,출고현황!$M$3:$M$302,0)),""))</f>
-        <v/>
+        <v>168000</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15293,7 +15377,7 @@
       <c r="F29" s="25"/>
       <c r="G29" s="30" t="n">
         <f aca="false">SUM(G11:G28)</f>
-        <v>0</v>
+        <v>1668000</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15306,7 +15390,7 @@
       <c r="F30" s="25"/>
       <c r="G30" s="30" t="n">
         <f aca="false">ROUND(G29*기초정보!$C$11,0)</f>
-        <v>0</v>
+        <v>166800</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15319,7 +15403,7 @@
       <c r="F31" s="31"/>
       <c r="G31" s="32" t="n">
         <f aca="false">G29+G30</f>
-        <v>0</v>
+        <v>1834800</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15403,9 +15487,9 @@
       <c r="E3" s="21" t="s">
         <v>62</v>
       </c>
-      <c r="F3" s="23" t="str">
+      <c r="F3" s="23" t="n">
         <f aca="false">IFERROR(INDEX(출고현황!$B$3:$B$302,MATCH($C$3,출고현황!$A$3:$A$302,0)),"")</f>
-        <v/>
+        <v>46267</v>
       </c>
       <c r="G3" s="23"/>
     </row>
@@ -15427,7 +15511,7 @@
       <c r="B6" s="25"/>
       <c r="C6" s="18" t="str">
         <f aca="false">IFERROR(INDEX(출고현황!$C$3:$C$302,MATCH($C$3,출고현황!$A$3:$A$302,0)),"")</f>
-        <v/>
+        <v>○○전자</v>
       </c>
       <c r="D6" s="18"/>
       <c r="E6" s="25" t="s">
@@ -15446,7 +15530,7 @@
       <c r="B7" s="25"/>
       <c r="C7" s="18" t="str">
         <f aca="false">IFERROR(INDEX(거래처목록!$B$3:$B$62,MATCH($C$6,거래처목록!$A$3:$A$62,0)),"")</f>
-        <v/>
+        <v>111-11-11111</v>
       </c>
       <c r="D7" s="18"/>
       <c r="E7" s="25" t="s">
@@ -15465,7 +15549,7 @@
       <c r="B8" s="25"/>
       <c r="C8" s="18" t="str">
         <f aca="false">IFERROR(INDEX(거래처목록!$E$3:$E$62,MATCH($C$6,거래처목록!$A$3:$A$62,0)),"")</f>
-        <v/>
+        <v>박과장</v>
       </c>
       <c r="D8" s="18"/>
       <c r="E8" s="25" t="s">
